--- a/Data/testDataUK_IDGenerator.xlsx
+++ b/Data/testDataUK_IDGenerator.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1196A3D7-9937-4B05-835A-184462BEC768}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{856E0F4E-7E67-44FA-88F0-95EE773ED8A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1068" yWindow="-108" windowWidth="22080" windowHeight="13176" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1194" uniqueCount="345">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1284" uniqueCount="375">
   <si>
     <t>TestCaseIDs</t>
   </si>
@@ -1077,6 +1077,96 @@
   </si>
   <si>
     <t>AB911819A</t>
+  </si>
+  <si>
+    <t>AB911820A</t>
+  </si>
+  <si>
+    <t>AB911821A</t>
+  </si>
+  <si>
+    <t>AB911822A</t>
+  </si>
+  <si>
+    <t>AB911823A</t>
+  </si>
+  <si>
+    <t>AB911824A</t>
+  </si>
+  <si>
+    <t>AB911825A</t>
+  </si>
+  <si>
+    <t>AB911826A</t>
+  </si>
+  <si>
+    <t>AB911827A</t>
+  </si>
+  <si>
+    <t>AB911828A</t>
+  </si>
+  <si>
+    <t>AB911829A</t>
+  </si>
+  <si>
+    <t>AB911830A</t>
+  </si>
+  <si>
+    <t>AB911831A</t>
+  </si>
+  <si>
+    <t>AB911832A</t>
+  </si>
+  <si>
+    <t>AB911833A</t>
+  </si>
+  <si>
+    <t>AB911834A</t>
+  </si>
+  <si>
+    <t>AB911835A</t>
+  </si>
+  <si>
+    <t>AB911836A</t>
+  </si>
+  <si>
+    <t>AB911837A</t>
+  </si>
+  <si>
+    <t>AB911838A</t>
+  </si>
+  <si>
+    <t>AB911839A</t>
+  </si>
+  <si>
+    <t>AB911840A</t>
+  </si>
+  <si>
+    <t>AB911841A</t>
+  </si>
+  <si>
+    <t>AB911842A</t>
+  </si>
+  <si>
+    <t>AB911843A</t>
+  </si>
+  <si>
+    <t>AB911844A</t>
+  </si>
+  <si>
+    <t>AB911845A</t>
+  </si>
+  <si>
+    <t>AB911846A</t>
+  </si>
+  <si>
+    <t>AB911847A</t>
+  </si>
+  <si>
+    <t>AB911848A</t>
+  </si>
+  <si>
+    <t>AB911849A</t>
   </si>
 </sst>
 </file>
@@ -4805,7 +4895,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{817E4E34-4D65-4931-861C-871B7875EF5F}">
-  <dimension ref="A1:G115"/>
+  <dimension ref="A1:G145"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
@@ -6745,7 +6835,7 @@
         <v>240</v>
       </c>
       <c r="E108" t="str">
-        <f t="shared" ref="E108:E115" si="5">A108&amp;B108&amp;C108</f>
+        <f t="shared" ref="E108:E128" si="5">A108&amp;B108&amp;C108</f>
         <v>AB911812A</v>
       </c>
       <c r="G108" s="29" t="s">
@@ -6876,6 +6966,546 @@
       </c>
       <c r="G115" s="29" t="s">
         <v>344</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A116" t="s">
+        <v>239</v>
+      </c>
+      <c r="B116">
+        <v>911820</v>
+      </c>
+      <c r="C116" t="s">
+        <v>240</v>
+      </c>
+      <c r="E116" t="str">
+        <f t="shared" si="5"/>
+        <v>AB911820A</v>
+      </c>
+      <c r="G116" s="29" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A117" t="s">
+        <v>239</v>
+      </c>
+      <c r="B117">
+        <v>911821</v>
+      </c>
+      <c r="C117" t="s">
+        <v>240</v>
+      </c>
+      <c r="E117" t="str">
+        <f t="shared" si="5"/>
+        <v>AB911821A</v>
+      </c>
+      <c r="G117" s="29" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A118" t="s">
+        <v>239</v>
+      </c>
+      <c r="B118">
+        <v>911822</v>
+      </c>
+      <c r="C118" t="s">
+        <v>240</v>
+      </c>
+      <c r="E118" t="str">
+        <f t="shared" si="5"/>
+        <v>AB911822A</v>
+      </c>
+      <c r="G118" s="29" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A119" t="s">
+        <v>239</v>
+      </c>
+      <c r="B119">
+        <v>911823</v>
+      </c>
+      <c r="C119" t="s">
+        <v>240</v>
+      </c>
+      <c r="E119" t="str">
+        <f t="shared" si="5"/>
+        <v>AB911823A</v>
+      </c>
+      <c r="G119" s="29" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A120" t="s">
+        <v>239</v>
+      </c>
+      <c r="B120">
+        <v>911824</v>
+      </c>
+      <c r="C120" t="s">
+        <v>240</v>
+      </c>
+      <c r="E120" t="str">
+        <f t="shared" si="5"/>
+        <v>AB911824A</v>
+      </c>
+      <c r="G120" s="29" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A121" t="s">
+        <v>239</v>
+      </c>
+      <c r="B121">
+        <v>911825</v>
+      </c>
+      <c r="C121" t="s">
+        <v>240</v>
+      </c>
+      <c r="E121" t="str">
+        <f t="shared" si="5"/>
+        <v>AB911825A</v>
+      </c>
+      <c r="G121" s="29" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A122" t="s">
+        <v>239</v>
+      </c>
+      <c r="B122">
+        <v>911826</v>
+      </c>
+      <c r="C122" t="s">
+        <v>240</v>
+      </c>
+      <c r="E122" t="str">
+        <f t="shared" si="5"/>
+        <v>AB911826A</v>
+      </c>
+      <c r="G122" s="29" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A123" t="s">
+        <v>239</v>
+      </c>
+      <c r="B123">
+        <v>911827</v>
+      </c>
+      <c r="C123" t="s">
+        <v>240</v>
+      </c>
+      <c r="E123" t="str">
+        <f t="shared" si="5"/>
+        <v>AB911827A</v>
+      </c>
+      <c r="G123" s="29" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A124" t="s">
+        <v>239</v>
+      </c>
+      <c r="B124">
+        <v>911828</v>
+      </c>
+      <c r="C124" t="s">
+        <v>240</v>
+      </c>
+      <c r="E124" t="str">
+        <f t="shared" si="5"/>
+        <v>AB911828A</v>
+      </c>
+      <c r="G124" s="29" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A125" t="s">
+        <v>239</v>
+      </c>
+      <c r="B125">
+        <v>911829</v>
+      </c>
+      <c r="C125" t="s">
+        <v>240</v>
+      </c>
+      <c r="E125" t="str">
+        <f t="shared" si="5"/>
+        <v>AB911829A</v>
+      </c>
+      <c r="G125" s="29" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A126" t="s">
+        <v>239</v>
+      </c>
+      <c r="B126">
+        <v>911830</v>
+      </c>
+      <c r="C126" t="s">
+        <v>240</v>
+      </c>
+      <c r="E126" t="str">
+        <f t="shared" si="5"/>
+        <v>AB911830A</v>
+      </c>
+      <c r="G126" s="29" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A127" t="s">
+        <v>239</v>
+      </c>
+      <c r="B127">
+        <v>911831</v>
+      </c>
+      <c r="C127" t="s">
+        <v>240</v>
+      </c>
+      <c r="E127" t="str">
+        <f t="shared" si="5"/>
+        <v>AB911831A</v>
+      </c>
+      <c r="G127" s="29" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A128" t="s">
+        <v>239</v>
+      </c>
+      <c r="B128">
+        <v>911832</v>
+      </c>
+      <c r="C128" t="s">
+        <v>240</v>
+      </c>
+      <c r="E128" t="str">
+        <f t="shared" si="5"/>
+        <v>AB911832A</v>
+      </c>
+      <c r="G128" s="29" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A129" t="s">
+        <v>239</v>
+      </c>
+      <c r="B129">
+        <v>911833</v>
+      </c>
+      <c r="C129" t="s">
+        <v>240</v>
+      </c>
+      <c r="E129" t="str">
+        <f t="shared" ref="E129:E144" si="6">A129&amp;B129&amp;C129</f>
+        <v>AB911833A</v>
+      </c>
+      <c r="G129" s="29" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A130" t="s">
+        <v>239</v>
+      </c>
+      <c r="B130">
+        <v>911834</v>
+      </c>
+      <c r="C130" t="s">
+        <v>240</v>
+      </c>
+      <c r="E130" t="str">
+        <f t="shared" si="6"/>
+        <v>AB911834A</v>
+      </c>
+      <c r="G130" s="29" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A131" t="s">
+        <v>239</v>
+      </c>
+      <c r="B131">
+        <v>911835</v>
+      </c>
+      <c r="C131" t="s">
+        <v>240</v>
+      </c>
+      <c r="E131" t="str">
+        <f t="shared" si="6"/>
+        <v>AB911835A</v>
+      </c>
+      <c r="G131" s="29" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A132" t="s">
+        <v>239</v>
+      </c>
+      <c r="B132">
+        <v>911836</v>
+      </c>
+      <c r="C132" t="s">
+        <v>240</v>
+      </c>
+      <c r="E132" t="str">
+        <f t="shared" si="6"/>
+        <v>AB911836A</v>
+      </c>
+      <c r="G132" s="29" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A133" t="s">
+        <v>239</v>
+      </c>
+      <c r="B133">
+        <v>911837</v>
+      </c>
+      <c r="C133" t="s">
+        <v>240</v>
+      </c>
+      <c r="E133" t="str">
+        <f t="shared" si="6"/>
+        <v>AB911837A</v>
+      </c>
+      <c r="G133" s="29" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A134" t="s">
+        <v>239</v>
+      </c>
+      <c r="B134">
+        <v>911838</v>
+      </c>
+      <c r="C134" t="s">
+        <v>240</v>
+      </c>
+      <c r="E134" t="str">
+        <f t="shared" si="6"/>
+        <v>AB911838A</v>
+      </c>
+      <c r="G134" s="29" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A135" t="s">
+        <v>239</v>
+      </c>
+      <c r="B135">
+        <v>911839</v>
+      </c>
+      <c r="C135" t="s">
+        <v>240</v>
+      </c>
+      <c r="E135" t="str">
+        <f t="shared" si="6"/>
+        <v>AB911839A</v>
+      </c>
+      <c r="G135" s="29" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A136" t="s">
+        <v>239</v>
+      </c>
+      <c r="B136">
+        <v>911840</v>
+      </c>
+      <c r="C136" t="s">
+        <v>240</v>
+      </c>
+      <c r="E136" t="str">
+        <f t="shared" si="6"/>
+        <v>AB911840A</v>
+      </c>
+      <c r="G136" s="29" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A137" t="s">
+        <v>239</v>
+      </c>
+      <c r="B137">
+        <v>911841</v>
+      </c>
+      <c r="C137" t="s">
+        <v>240</v>
+      </c>
+      <c r="E137" t="str">
+        <f t="shared" si="6"/>
+        <v>AB911841A</v>
+      </c>
+      <c r="G137" s="29" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A138" t="s">
+        <v>239</v>
+      </c>
+      <c r="B138">
+        <v>911842</v>
+      </c>
+      <c r="C138" t="s">
+        <v>240</v>
+      </c>
+      <c r="E138" t="str">
+        <f t="shared" si="6"/>
+        <v>AB911842A</v>
+      </c>
+      <c r="G138" s="29" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A139" t="s">
+        <v>239</v>
+      </c>
+      <c r="B139">
+        <v>911843</v>
+      </c>
+      <c r="C139" t="s">
+        <v>240</v>
+      </c>
+      <c r="E139" t="str">
+        <f t="shared" si="6"/>
+        <v>AB911843A</v>
+      </c>
+      <c r="G139" s="29" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A140" t="s">
+        <v>239</v>
+      </c>
+      <c r="B140">
+        <v>911844</v>
+      </c>
+      <c r="C140" t="s">
+        <v>240</v>
+      </c>
+      <c r="E140" t="str">
+        <f t="shared" si="6"/>
+        <v>AB911844A</v>
+      </c>
+      <c r="G140" s="29" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A141" t="s">
+        <v>239</v>
+      </c>
+      <c r="B141">
+        <v>911845</v>
+      </c>
+      <c r="C141" t="s">
+        <v>240</v>
+      </c>
+      <c r="E141" t="str">
+        <f t="shared" si="6"/>
+        <v>AB911845A</v>
+      </c>
+      <c r="G141" s="29" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A142" t="s">
+        <v>239</v>
+      </c>
+      <c r="B142">
+        <v>911846</v>
+      </c>
+      <c r="C142" t="s">
+        <v>240</v>
+      </c>
+      <c r="E142" t="str">
+        <f t="shared" si="6"/>
+        <v>AB911846A</v>
+      </c>
+      <c r="G142" s="29" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A143" t="s">
+        <v>239</v>
+      </c>
+      <c r="B143">
+        <v>911847</v>
+      </c>
+      <c r="C143" t="s">
+        <v>240</v>
+      </c>
+      <c r="E143" t="str">
+        <f t="shared" si="6"/>
+        <v>AB911847A</v>
+      </c>
+      <c r="G143" s="29" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A144" t="s">
+        <v>239</v>
+      </c>
+      <c r="B144">
+        <v>911848</v>
+      </c>
+      <c r="C144" t="s">
+        <v>240</v>
+      </c>
+      <c r="E144" t="str">
+        <f t="shared" si="6"/>
+        <v>AB911848A</v>
+      </c>
+      <c r="G144" s="29" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A145" t="s">
+        <v>239</v>
+      </c>
+      <c r="B145">
+        <v>911849</v>
+      </c>
+      <c r="C145" t="s">
+        <v>240</v>
+      </c>
+      <c r="E145" t="str">
+        <f t="shared" ref="E145" si="7">A145&amp;B145&amp;C145</f>
+        <v>AB911849A</v>
+      </c>
+      <c r="G145" s="29" t="s">
+        <v>374</v>
       </c>
     </row>
   </sheetData>

--- a/Data/testDataUK_IDGenerator.xlsx
+++ b/Data/testDataUK_IDGenerator.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{856E0F4E-7E67-44FA-88F0-95EE773ED8A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E2363C3-71E7-4C94-A04C-5B53CF847608}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1068" yWindow="-108" windowWidth="22080" windowHeight="13176" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1284" uniqueCount="375">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1374" uniqueCount="405">
   <si>
     <t>TestCaseIDs</t>
   </si>
@@ -1167,6 +1167,96 @@
   </si>
   <si>
     <t>AB911849A</t>
+  </si>
+  <si>
+    <t>AB911850A</t>
+  </si>
+  <si>
+    <t>AB911851A</t>
+  </si>
+  <si>
+    <t>AB911852A</t>
+  </si>
+  <si>
+    <t>AB911853A</t>
+  </si>
+  <si>
+    <t>AB911854A</t>
+  </si>
+  <si>
+    <t>AB911855A</t>
+  </si>
+  <si>
+    <t>AB911856A</t>
+  </si>
+  <si>
+    <t>AB911857A</t>
+  </si>
+  <si>
+    <t>AB911858A</t>
+  </si>
+  <si>
+    <t>AB911859A</t>
+  </si>
+  <si>
+    <t>AB911860A</t>
+  </si>
+  <si>
+    <t>AB911861A</t>
+  </si>
+  <si>
+    <t>AB911862A</t>
+  </si>
+  <si>
+    <t>AB911863A</t>
+  </si>
+  <si>
+    <t>AB911864A</t>
+  </si>
+  <si>
+    <t>AB911865A</t>
+  </si>
+  <si>
+    <t>AB911866A</t>
+  </si>
+  <si>
+    <t>AB911867A</t>
+  </si>
+  <si>
+    <t>AB911868A</t>
+  </si>
+  <si>
+    <t>AB911869A</t>
+  </si>
+  <si>
+    <t>AB911870A</t>
+  </si>
+  <si>
+    <t>AB911871A</t>
+  </si>
+  <si>
+    <t>AB911872A</t>
+  </si>
+  <si>
+    <t>AB911873A</t>
+  </si>
+  <si>
+    <t>AB911874A</t>
+  </si>
+  <si>
+    <t>AB911875A</t>
+  </si>
+  <si>
+    <t>AB911876A</t>
+  </si>
+  <si>
+    <t>AB911877A</t>
+  </si>
+  <si>
+    <t>AB911878A</t>
+  </si>
+  <si>
+    <t>AB911879A</t>
   </si>
 </sst>
 </file>
@@ -4895,7 +4985,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{817E4E34-4D65-4931-861C-871B7875EF5F}">
-  <dimension ref="A1:G145"/>
+  <dimension ref="A1:G176"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
@@ -7501,11 +7591,557 @@
         <v>240</v>
       </c>
       <c r="E145" t="str">
-        <f t="shared" ref="E145" si="7">A145&amp;B145&amp;C145</f>
+        <f t="shared" ref="E145:E176" si="7">A145&amp;B145&amp;C145</f>
         <v>AB911849A</v>
       </c>
       <c r="G145" s="29" t="s">
         <v>374</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A146" t="s">
+        <v>239</v>
+      </c>
+      <c r="B146">
+        <v>911850</v>
+      </c>
+      <c r="C146" t="s">
+        <v>240</v>
+      </c>
+      <c r="E146" t="str">
+        <f t="shared" si="7"/>
+        <v>AB911850A</v>
+      </c>
+      <c r="G146" s="29" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A147" t="s">
+        <v>239</v>
+      </c>
+      <c r="B147">
+        <v>911851</v>
+      </c>
+      <c r="C147" t="s">
+        <v>240</v>
+      </c>
+      <c r="E147" t="str">
+        <f t="shared" si="7"/>
+        <v>AB911851A</v>
+      </c>
+      <c r="G147" s="29" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A148" t="s">
+        <v>239</v>
+      </c>
+      <c r="B148">
+        <v>911852</v>
+      </c>
+      <c r="C148" t="s">
+        <v>240</v>
+      </c>
+      <c r="E148" t="str">
+        <f t="shared" si="7"/>
+        <v>AB911852A</v>
+      </c>
+      <c r="G148" s="29" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A149" t="s">
+        <v>239</v>
+      </c>
+      <c r="B149">
+        <v>911853</v>
+      </c>
+      <c r="C149" t="s">
+        <v>240</v>
+      </c>
+      <c r="E149" t="str">
+        <f t="shared" si="7"/>
+        <v>AB911853A</v>
+      </c>
+      <c r="G149" s="29" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A150" t="s">
+        <v>239</v>
+      </c>
+      <c r="B150">
+        <v>911854</v>
+      </c>
+      <c r="C150" t="s">
+        <v>240</v>
+      </c>
+      <c r="E150" t="str">
+        <f t="shared" si="7"/>
+        <v>AB911854A</v>
+      </c>
+      <c r="G150" s="29" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A151" t="s">
+        <v>239</v>
+      </c>
+      <c r="B151">
+        <v>911855</v>
+      </c>
+      <c r="C151" t="s">
+        <v>240</v>
+      </c>
+      <c r="E151" t="str">
+        <f t="shared" si="7"/>
+        <v>AB911855A</v>
+      </c>
+      <c r="G151" s="29" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A152" t="s">
+        <v>239</v>
+      </c>
+      <c r="B152">
+        <v>911856</v>
+      </c>
+      <c r="C152" t="s">
+        <v>240</v>
+      </c>
+      <c r="E152" t="str">
+        <f t="shared" si="7"/>
+        <v>AB911856A</v>
+      </c>
+      <c r="G152" s="29" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A153" t="s">
+        <v>239</v>
+      </c>
+      <c r="B153">
+        <v>911857</v>
+      </c>
+      <c r="C153" t="s">
+        <v>240</v>
+      </c>
+      <c r="E153" t="str">
+        <f t="shared" si="7"/>
+        <v>AB911857A</v>
+      </c>
+      <c r="G153" s="29" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A154" t="s">
+        <v>239</v>
+      </c>
+      <c r="B154">
+        <v>911858</v>
+      </c>
+      <c r="C154" t="s">
+        <v>240</v>
+      </c>
+      <c r="E154" t="str">
+        <f t="shared" si="7"/>
+        <v>AB911858A</v>
+      </c>
+      <c r="G154" s="29" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A155" t="s">
+        <v>239</v>
+      </c>
+      <c r="B155">
+        <v>911859</v>
+      </c>
+      <c r="C155" t="s">
+        <v>240</v>
+      </c>
+      <c r="E155" t="str">
+        <f t="shared" si="7"/>
+        <v>AB911859A</v>
+      </c>
+      <c r="G155" s="29" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A156" t="s">
+        <v>239</v>
+      </c>
+      <c r="B156">
+        <v>911860</v>
+      </c>
+      <c r="C156" t="s">
+        <v>240</v>
+      </c>
+      <c r="E156" t="str">
+        <f t="shared" si="7"/>
+        <v>AB911860A</v>
+      </c>
+      <c r="G156" s="29" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A157" t="s">
+        <v>239</v>
+      </c>
+      <c r="B157">
+        <v>911861</v>
+      </c>
+      <c r="C157" t="s">
+        <v>240</v>
+      </c>
+      <c r="E157" t="str">
+        <f t="shared" si="7"/>
+        <v>AB911861A</v>
+      </c>
+      <c r="G157" s="29" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A158" t="s">
+        <v>239</v>
+      </c>
+      <c r="B158">
+        <v>911862</v>
+      </c>
+      <c r="C158" t="s">
+        <v>240</v>
+      </c>
+      <c r="E158" t="str">
+        <f t="shared" si="7"/>
+        <v>AB911862A</v>
+      </c>
+      <c r="G158" s="29" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A159" t="s">
+        <v>239</v>
+      </c>
+      <c r="B159">
+        <v>911863</v>
+      </c>
+      <c r="C159" t="s">
+        <v>240</v>
+      </c>
+      <c r="E159" t="str">
+        <f t="shared" si="7"/>
+        <v>AB911863A</v>
+      </c>
+      <c r="G159" s="29" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="160" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A160" t="s">
+        <v>239</v>
+      </c>
+      <c r="B160">
+        <v>911864</v>
+      </c>
+      <c r="C160" t="s">
+        <v>240</v>
+      </c>
+      <c r="E160" t="str">
+        <f t="shared" si="7"/>
+        <v>AB911864A</v>
+      </c>
+      <c r="G160" s="29" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="161" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A161" t="s">
+        <v>239</v>
+      </c>
+      <c r="B161">
+        <v>911865</v>
+      </c>
+      <c r="C161" t="s">
+        <v>240</v>
+      </c>
+      <c r="E161" t="str">
+        <f t="shared" si="7"/>
+        <v>AB911865A</v>
+      </c>
+      <c r="G161" s="29" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A162" t="s">
+        <v>239</v>
+      </c>
+      <c r="B162">
+        <v>911866</v>
+      </c>
+      <c r="C162" t="s">
+        <v>240</v>
+      </c>
+      <c r="E162" t="str">
+        <f t="shared" si="7"/>
+        <v>AB911866A</v>
+      </c>
+      <c r="G162" s="29" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A163" t="s">
+        <v>239</v>
+      </c>
+      <c r="B163">
+        <v>911867</v>
+      </c>
+      <c r="C163" t="s">
+        <v>240</v>
+      </c>
+      <c r="E163" t="str">
+        <f t="shared" si="7"/>
+        <v>AB911867A</v>
+      </c>
+      <c r="G163" s="29" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A164" t="s">
+        <v>239</v>
+      </c>
+      <c r="B164">
+        <v>911868</v>
+      </c>
+      <c r="C164" t="s">
+        <v>240</v>
+      </c>
+      <c r="E164" t="str">
+        <f t="shared" si="7"/>
+        <v>AB911868A</v>
+      </c>
+      <c r="G164" s="29" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="165" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A165" t="s">
+        <v>239</v>
+      </c>
+      <c r="B165">
+        <v>911869</v>
+      </c>
+      <c r="C165" t="s">
+        <v>240</v>
+      </c>
+      <c r="E165" t="str">
+        <f t="shared" si="7"/>
+        <v>AB911869A</v>
+      </c>
+      <c r="G165" s="29" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="166" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A166" t="s">
+        <v>239</v>
+      </c>
+      <c r="B166">
+        <v>911870</v>
+      </c>
+      <c r="C166" t="s">
+        <v>240</v>
+      </c>
+      <c r="E166" t="str">
+        <f t="shared" si="7"/>
+        <v>AB911870A</v>
+      </c>
+      <c r="G166" s="29" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="167" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A167" t="s">
+        <v>239</v>
+      </c>
+      <c r="B167">
+        <v>911871</v>
+      </c>
+      <c r="C167" t="s">
+        <v>240</v>
+      </c>
+      <c r="E167" t="str">
+        <f t="shared" si="7"/>
+        <v>AB911871A</v>
+      </c>
+      <c r="G167" s="29" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="168" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A168" t="s">
+        <v>239</v>
+      </c>
+      <c r="B168">
+        <v>911872</v>
+      </c>
+      <c r="C168" t="s">
+        <v>240</v>
+      </c>
+      <c r="E168" t="str">
+        <f t="shared" si="7"/>
+        <v>AB911872A</v>
+      </c>
+      <c r="G168" s="29" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="169" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A169" t="s">
+        <v>239</v>
+      </c>
+      <c r="B169">
+        <v>911873</v>
+      </c>
+      <c r="C169" t="s">
+        <v>240</v>
+      </c>
+      <c r="E169" t="str">
+        <f t="shared" si="7"/>
+        <v>AB911873A</v>
+      </c>
+      <c r="G169" s="29" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="170" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A170" t="s">
+        <v>239</v>
+      </c>
+      <c r="B170">
+        <v>911874</v>
+      </c>
+      <c r="C170" t="s">
+        <v>240</v>
+      </c>
+      <c r="E170" t="str">
+        <f t="shared" si="7"/>
+        <v>AB911874A</v>
+      </c>
+      <c r="G170" s="29" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="171" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A171" t="s">
+        <v>239</v>
+      </c>
+      <c r="B171">
+        <v>911875</v>
+      </c>
+      <c r="C171" t="s">
+        <v>240</v>
+      </c>
+      <c r="E171" t="str">
+        <f t="shared" si="7"/>
+        <v>AB911875A</v>
+      </c>
+      <c r="G171" s="29" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="172" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A172" t="s">
+        <v>239</v>
+      </c>
+      <c r="B172">
+        <v>911876</v>
+      </c>
+      <c r="C172" t="s">
+        <v>240</v>
+      </c>
+      <c r="E172" t="str">
+        <f t="shared" si="7"/>
+        <v>AB911876A</v>
+      </c>
+      <c r="G172" s="29" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="173" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A173" t="s">
+        <v>239</v>
+      </c>
+      <c r="B173">
+        <v>911877</v>
+      </c>
+      <c r="C173" t="s">
+        <v>240</v>
+      </c>
+      <c r="E173" t="str">
+        <f t="shared" si="7"/>
+        <v>AB911877A</v>
+      </c>
+      <c r="G173" s="29" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="174" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A174" t="s">
+        <v>239</v>
+      </c>
+      <c r="B174">
+        <v>911878</v>
+      </c>
+      <c r="C174" t="s">
+        <v>240</v>
+      </c>
+      <c r="E174" t="str">
+        <f t="shared" si="7"/>
+        <v>AB911878A</v>
+      </c>
+      <c r="G174" s="29" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="175" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A175" t="s">
+        <v>239</v>
+      </c>
+      <c r="B175">
+        <v>911879</v>
+      </c>
+      <c r="C175" t="s">
+        <v>240</v>
+      </c>
+      <c r="E175" t="str">
+        <f t="shared" si="7"/>
+        <v>AB911879A</v>
+      </c>
+      <c r="G175" s="29" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="176" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="E176" t="str">
+        <f t="shared" si="7"/>
+        <v/>
       </c>
     </row>
   </sheetData>
